--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-7.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F32028FB-FF1C-4D46-BDD4-577843B13624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43E9092D-97E8-4846-AEBF-BED83B533933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{4CF87429-A380-4413-AF01-482A91D022E9}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{E3D8748A-E52D-45CA-A052-C070203077CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="183" r:id="rId3"/>
+    <pivotCache cacheId="215" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576915972226" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{F9BEA298-1A5D-4D0B-A6D9-6CD268C68E42}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579485995368" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{B10EEFF2-DABD-4D16-B03F-256C889D7235}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{529E3BF1-3D84-48C3-A399-D2A4847D336B}" name="AllErrorPivot" cacheId="183" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A87B230D-E20D-4650-830D-D663F7658AAE}" name="AllErrorPivot" cacheId="215" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -585,7 +585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CDF7B6-9667-4D95-B8B7-C3A0371D4C9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68721AD-40E1-48E4-8063-F303EDF44CDA}">
   <dimension ref="A4:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -671,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D03727-16BF-403F-9210-B0453F6E8074}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B325A2-BDBD-482A-97AF-470123AC3A1C}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
